--- a/17 18 20/2 Tableau/6.Data Modeling/2.Joins/1.Simple Joins/Data/JoinTableMultyColumns.xlsx
+++ b/17 18 20/2 Tableau/6.Data Modeling/2.Joins/1.Simple Joins/Data/JoinTableMultyColumns.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="LeftTable" sheetId="1" r:id="rId1"/>

--- a/17 18 20/2 Tableau/6.Data Modeling/2.Joins/1.Simple Joins/Data/JoinTableMultyColumns.xlsx
+++ b/17 18 20/2 Tableau/6.Data Modeling/2.Joins/1.Simple Joins/Data/JoinTableMultyColumns.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LeftTable" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>emp_id</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>AREA</t>
-  </si>
-  <si>
-    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -135,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -144,6 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +433,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -550,6 +548,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -568,8 +567,8 @@
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>23</v>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
